--- a/programs/2026-10_India_Pilot_2/program.xlsx
+++ b/programs/2026-10_India_Pilot_2/program.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Authentica\Presales\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/20baf977624bf256/Documents/GitHub/MondayProgramSync/MondayProgramSync/programs/2026-10_India_Pilot_2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{320A2FC3-4A92-4980-AE71-ADA670317387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{320A2FC3-4A92-4980-AE71-ADA670317387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0345B7B0-0FCF-4BF4-9FAE-DF7BEF9B7748}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2218,6 +2218,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="32" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2225,9 +2228,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="32" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2590,7 +2590,7 @@
         <v>116</v>
       </c>
       <c r="C5" s="44">
-        <v>46266</v>
+        <v>46082</v>
       </c>
       <c r="D5" s="124" t="s">
         <v>156</v>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="C7" s="44">
         <f>$C$5+14</f>
-        <v>46280</v>
+        <v>46096</v>
       </c>
       <c r="D7" s="126" t="s">
         <v>155</v>
@@ -2647,7 +2647,7 @@
         <v>137</v>
       </c>
       <c r="C9" s="44">
-        <v>46296</v>
+        <v>46101</v>
       </c>
       <c r="D9" s="124" t="s">
         <v>157</v>
@@ -2675,7 +2675,7 @@
         <v>127</v>
       </c>
       <c r="C11" s="44">
-        <v>46357</v>
+        <v>46130</v>
       </c>
       <c r="D11" s="124" t="s">
         <v>158</v>
@@ -2692,7 +2692,7 @@
         <v>162</v>
       </c>
       <c r="C12" s="44">
-        <v>46368</v>
+        <v>46234</v>
       </c>
       <c r="D12" s="124" t="s">
         <v>163</v>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="C5" s="83">
         <f>Legend!$C$5</f>
-        <v>46266</v>
+        <v>46082</v>
       </c>
       <c r="D5" s="83" t="s">
         <v>274</v>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="C6" s="84">
         <f>Legend!$C$5+1</f>
-        <v>46267</v>
+        <v>46083</v>
       </c>
       <c r="D6" s="84" t="s">
         <v>274</v>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="C7" s="84">
         <f>Legend!$C$5+1</f>
-        <v>46267</v>
+        <v>46083</v>
       </c>
       <c r="D7" s="84" t="s">
         <v>274</v>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="C8" s="85">
         <f>Legend!$C$5+7</f>
-        <v>46273</v>
+        <v>46089</v>
       </c>
       <c r="D8" s="85" t="s">
         <v>274</v>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="C9" s="85">
         <f>Legend!$C$5+7</f>
-        <v>46273</v>
+        <v>46089</v>
       </c>
       <c r="D9" s="85" t="s">
         <v>274</v>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="C10" s="86">
         <f>Legend!$C$5+7</f>
-        <v>46273</v>
+        <v>46089</v>
       </c>
       <c r="D10" s="86" t="s">
         <v>274</v>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C11" s="86">
         <f>Legend!$C$5+7</f>
-        <v>46273</v>
+        <v>46089</v>
       </c>
       <c r="D11" s="86" t="s">
         <v>274</v>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="C12" s="85">
         <f>Legend!$C$5+7</f>
-        <v>46273</v>
+        <v>46089</v>
       </c>
       <c r="D12" s="85" t="s">
         <v>274</v>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="C13" s="87">
         <f>Legend!$C$7-1</f>
-        <v>46279</v>
+        <v>46095</v>
       </c>
       <c r="D13" s="87" t="s">
         <v>274</v>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="C14" s="88">
         <f>Legend!$C$7-1</f>
-        <v>46279</v>
+        <v>46095</v>
       </c>
       <c r="D14" s="88" t="s">
         <v>274</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="C15" s="89">
         <f>Legend!$C$7</f>
-        <v>46280</v>
+        <v>46096</v>
       </c>
       <c r="D15" s="89" t="s">
         <v>274</v>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="C16" s="90">
         <f>Legend!$C$7+15</f>
-        <v>46295</v>
+        <v>46111</v>
       </c>
       <c r="D16" s="90" t="s">
         <v>274</v>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="C21" s="92">
         <f>Legend!$C$11-90</f>
-        <v>46267</v>
+        <v>46040</v>
       </c>
       <c r="D21" s="92" t="s">
         <v>277</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C22" s="93">
         <f>Legend!$C$9+1</f>
-        <v>46297</v>
+        <v>46102</v>
       </c>
       <c r="D22" s="93" t="s">
         <v>277</v>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="C23" s="94">
         <f>Legend!$C$9+3</f>
-        <v>46299</v>
+        <v>46104</v>
       </c>
       <c r="D23" s="94" t="s">
         <v>277</v>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="C24" s="94">
         <f>Legend!$C$9+3</f>
-        <v>46299</v>
+        <v>46104</v>
       </c>
       <c r="D24" s="94" t="s">
         <v>277</v>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="C25" s="95">
         <f>Legend!$C$9+7</f>
-        <v>46303</v>
+        <v>46108</v>
       </c>
       <c r="D25" s="95" t="s">
         <v>277</v>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="C26" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D26" s="96" t="s">
         <v>277</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C27" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D27" s="96" t="s">
         <v>277</v>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="C28" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D28" s="96" t="s">
         <v>277</v>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="C29" s="97">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D29" s="97" t="s">
         <v>277</v>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="C30" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D30" s="96" t="s">
         <v>277</v>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="C31" s="97">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D31" s="97" t="s">
         <v>277</v>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="C32" s="98">
         <f>Legend!$C$11-15</f>
-        <v>46342</v>
+        <v>46115</v>
       </c>
       <c r="D32" s="98" t="s">
         <v>275</v>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="C33" s="99">
         <f>Legend!$C$11-7</f>
-        <v>46350</v>
+        <v>46123</v>
       </c>
       <c r="D33" s="99" t="s">
         <v>275</v>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="C34" s="99">
         <f>Legend!$C$11-7</f>
-        <v>46350</v>
+        <v>46123</v>
       </c>
       <c r="D34" s="99" t="s">
         <v>275</v>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="C35" s="99">
         <f>Legend!$C$11-7</f>
-        <v>46350</v>
+        <v>46123</v>
       </c>
       <c r="D35" s="99" t="s">
         <v>275</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C36" s="100">
         <f>Legend!$C$11-1</f>
-        <v>46356</v>
+        <v>46129</v>
       </c>
       <c r="D36" s="100" t="s">
         <v>275</v>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="C37" s="101">
         <f>Legend!$C$11-7</f>
-        <v>46350</v>
+        <v>46123</v>
       </c>
       <c r="D37" s="101" t="s">
         <v>275</v>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="C38" s="101">
         <f>Legend!$C$11-7</f>
-        <v>46350</v>
+        <v>46123</v>
       </c>
       <c r="D38" s="101" t="s">
         <v>275</v>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="C39" s="102">
         <f>Legend!$C$12</f>
-        <v>46368</v>
+        <v>46234</v>
       </c>
       <c r="D39" s="102" t="s">
         <v>275</v>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="C40" s="102">
         <f>Legend!$C$12</f>
-        <v>46368</v>
+        <v>46234</v>
       </c>
       <c r="D40" s="102" t="s">
         <v>275</v>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="C45" s="103">
         <f>Legend!$C$5+45</f>
-        <v>46311</v>
+        <v>46127</v>
       </c>
       <c r="D45" s="103" t="s">
         <v>274</v>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="C46" s="103">
         <f>Legend!$C$5+45</f>
-        <v>46311</v>
+        <v>46127</v>
       </c>
       <c r="D46" s="103" t="s">
         <v>274</v>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="C47" s="104">
         <f>Legend!$C$5+40</f>
-        <v>46306</v>
+        <v>46122</v>
       </c>
       <c r="D47" s="104" t="s">
         <v>274</v>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="C48" s="105">
         <f>Legend!$C$5+35</f>
-        <v>46301</v>
+        <v>46117</v>
       </c>
       <c r="D48" s="105" t="s">
         <v>274</v>
@@ -3855,7 +3855,7 @@
       </c>
       <c r="C49" s="105">
         <f>Legend!$C$5+35</f>
-        <v>46301</v>
+        <v>46117</v>
       </c>
       <c r="D49" s="105" t="s">
         <v>274</v>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="C54" s="106">
         <f>Legend!$C$11-15</f>
-        <v>46342</v>
+        <v>46115</v>
       </c>
       <c r="D54" s="106" t="s">
         <v>277</v>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="C55" s="107">
         <f>Legend!$C$11-7</f>
-        <v>46350</v>
+        <v>46123</v>
       </c>
       <c r="D55" s="107" t="s">
         <v>277</v>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="C56" s="108">
         <f>Legend!$C$11-2</f>
-        <v>46355</v>
+        <v>46128</v>
       </c>
       <c r="D56" s="108" t="s">
         <v>275</v>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="C57" s="108">
         <f>Legend!$C$11-2</f>
-        <v>46355</v>
+        <v>46128</v>
       </c>
       <c r="D57" s="108" t="s">
         <v>275</v>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="C58" s="108">
         <f>Legend!$C$11-2</f>
-        <v>46355</v>
+        <v>46128</v>
       </c>
       <c r="D58" s="108" t="s">
         <v>275</v>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="C59" s="108">
         <f>Legend!$C$11-2</f>
-        <v>46355</v>
+        <v>46128</v>
       </c>
       <c r="D59" s="108" t="s">
         <v>275</v>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="C64" s="95">
         <f>Legend!$C$9+7</f>
-        <v>46303</v>
+        <v>46108</v>
       </c>
       <c r="D64" s="95" t="s">
         <v>277</v>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="C65" s="93">
         <f>Legend!$C$9+1</f>
-        <v>46297</v>
+        <v>46102</v>
       </c>
       <c r="D65" s="93" t="s">
         <v>277</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C66" s="95">
         <f>Legend!$C$9+7</f>
-        <v>46303</v>
+        <v>46108</v>
       </c>
       <c r="D66" s="95" t="s">
         <v>277</v>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="C67" s="110">
         <f>Legend!$C$9+30</f>
-        <v>46326</v>
+        <v>46131</v>
       </c>
       <c r="D67" s="110" t="s">
         <v>277</v>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="C68" s="110">
         <f>Legend!$C$9+30</f>
-        <v>46326</v>
+        <v>46131</v>
       </c>
       <c r="D68" s="110" t="s">
         <v>275</v>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="C69" s="98">
         <f>Legend!$C$11-15</f>
-        <v>46342</v>
+        <v>46115</v>
       </c>
       <c r="D69" s="98" t="s">
         <v>275</v>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="C70" s="106">
         <f>Legend!$C$11-15</f>
-        <v>46342</v>
+        <v>46115</v>
       </c>
       <c r="D70" s="106" t="s">
         <v>275</v>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C71" s="99">
         <f>Legend!$C$11-7</f>
-        <v>46350</v>
+        <v>46123</v>
       </c>
       <c r="D71" s="99" t="s">
         <v>275</v>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C72" s="100">
         <f>Legend!$C$11-1</f>
-        <v>46356</v>
+        <v>46129</v>
       </c>
       <c r="D72" s="100" t="s">
         <v>275</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="C73" s="101">
         <f>Legend!$C$11</f>
-        <v>46357</v>
+        <v>46130</v>
       </c>
       <c r="D73" s="101" t="s">
         <v>275</v>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="C74" s="102">
         <f>Legend!$C$12+7</f>
-        <v>46375</v>
+        <v>46241</v>
       </c>
       <c r="D74" s="102" t="s">
         <v>275</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="C79" s="93">
         <f>Legend!$C$9+1</f>
-        <v>46297</v>
+        <v>46102</v>
       </c>
       <c r="D79" s="93" t="s">
         <v>275</v>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C80" s="93">
         <f>Legend!$C$9+1</f>
-        <v>46297</v>
+        <v>46102</v>
       </c>
       <c r="D80" s="93" t="s">
         <v>275</v>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="C81" s="95">
         <f>Legend!$C$9+7</f>
-        <v>46303</v>
+        <v>46108</v>
       </c>
       <c r="D81" s="95" t="s">
         <v>275</v>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="C82" s="111">
         <f>Legend!$C$9+15</f>
-        <v>46311</v>
+        <v>46116</v>
       </c>
       <c r="D82" s="111" t="s">
         <v>275</v>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="C83" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D83" s="96" t="s">
         <v>275</v>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="C88" s="93">
         <f>Legend!$C$9+1</f>
-        <v>46297</v>
+        <v>46102</v>
       </c>
       <c r="D88" s="93" t="s">
         <v>277</v>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="C89" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D89" s="96" t="s">
         <v>277</v>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="C90" s="106">
         <f>Legend!$C$11-15</f>
-        <v>46342</v>
+        <v>46115</v>
       </c>
       <c r="D90" s="106" t="s">
         <v>275</v>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="C91" s="99">
         <f>Legend!$C$11-7</f>
-        <v>46350</v>
+        <v>46123</v>
       </c>
       <c r="D91" s="99" t="s">
         <v>275</v>
@@ -4777,7 +4777,7 @@
       </c>
       <c r="C92" s="100">
         <f>Legend!$C$11-1</f>
-        <v>46356</v>
+        <v>46129</v>
       </c>
       <c r="D92" s="100" t="s">
         <v>275</v>
@@ -4804,7 +4804,7 @@
       </c>
       <c r="C93" s="101">
         <f>Legend!$C$11</f>
-        <v>46357</v>
+        <v>46130</v>
       </c>
       <c r="D93" s="101" t="s">
         <v>275</v>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C94" s="102">
         <f>Legend!$C$12+7</f>
-        <v>46375</v>
+        <v>46241</v>
       </c>
       <c r="D94" s="102" t="s">
         <v>275</v>
@@ -4910,7 +4910,7 @@
       </c>
       <c r="C99" s="93">
         <f>Legend!$C$9+1</f>
-        <v>46297</v>
+        <v>46102</v>
       </c>
       <c r="D99" s="93" t="s">
         <v>274</v>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="C100" s="95">
         <f>Legend!$C$9+7</f>
-        <v>46303</v>
+        <v>46108</v>
       </c>
       <c r="D100" s="95" t="s">
         <v>274</v>
@@ -4964,7 +4964,7 @@
       </c>
       <c r="C101" s="111">
         <f>Legend!$C$9+15</f>
-        <v>46311</v>
+        <v>46116</v>
       </c>
       <c r="D101" s="111" t="s">
         <v>277</v>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="C102" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D102" s="96" t="s">
         <v>275</v>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="C103" s="98">
         <f>Legend!$C$11-15</f>
-        <v>46342</v>
+        <v>46115</v>
       </c>
       <c r="D103" s="98" t="s">
         <v>275</v>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="C104" s="99">
         <f>Legend!$C$11-7</f>
-        <v>46350</v>
+        <v>46123</v>
       </c>
       <c r="D104" s="99" t="s">
         <v>275</v>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="C105" s="100">
         <f>Legend!$C$11-1</f>
-        <v>46356</v>
+        <v>46129</v>
       </c>
       <c r="D105" s="100" t="s">
         <v>275</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="C110" s="112">
         <f>Legend!$C$5+1</f>
-        <v>46267</v>
+        <v>46083</v>
       </c>
       <c r="D110" s="112" t="s">
         <v>274</v>
@@ -5178,7 +5178,7 @@
       </c>
       <c r="C111" s="112">
         <f>Legend!$C$9</f>
-        <v>46296</v>
+        <v>46101</v>
       </c>
       <c r="D111" s="112" t="s">
         <v>277</v>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="C112" s="93">
         <f>Legend!$C$5+1</f>
-        <v>46267</v>
+        <v>46083</v>
       </c>
       <c r="D112" s="93" t="s">
         <v>274</v>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="C113" s="93">
         <f>Legend!$C$9+1</f>
-        <v>46297</v>
+        <v>46102</v>
       </c>
       <c r="D113" s="93" t="s">
         <v>277</v>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="C114" s="111">
         <f>Legend!$C$9+15</f>
-        <v>46311</v>
+        <v>46116</v>
       </c>
       <c r="D114" s="111" t="s">
         <v>277</v>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="C115" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D115" s="96" t="s">
         <v>277</v>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="C116" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D116" s="96" t="s">
         <v>275</v>
@@ -5332,7 +5332,7 @@
       </c>
       <c r="C117" s="98">
         <f>Legend!$C$11-15</f>
-        <v>46342</v>
+        <v>46115</v>
       </c>
       <c r="D117" s="98" t="s">
         <v>275</v>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="C118" s="99">
         <f>Legend!$C$11-7</f>
-        <v>46350</v>
+        <v>46123</v>
       </c>
       <c r="D118" s="99" t="s">
         <v>275</v>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="C119" s="100">
         <f>Legend!$C$11-1</f>
-        <v>46356</v>
+        <v>46129</v>
       </c>
       <c r="D119" s="100" t="s">
         <v>275</v>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C120" s="101">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D120" s="101" t="s">
         <v>275</v>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="C121" s="101">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D121" s="101" t="s">
         <v>275</v>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="C122" s="102">
         <f>Legend!$C$12+7</f>
-        <v>46375</v>
+        <v>46241</v>
       </c>
       <c r="D122" s="102" t="s">
         <v>275</v>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="C127" s="112">
         <f>Legend!$C$9</f>
-        <v>46296</v>
+        <v>46101</v>
       </c>
       <c r="D127" s="112" t="s">
         <v>277</v>
@@ -5573,7 +5573,7 @@
       </c>
       <c r="C128" s="95">
         <f>Legend!$C$9+7</f>
-        <v>46303</v>
+        <v>46108</v>
       </c>
       <c r="D128" s="95" t="s">
         <v>277</v>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="C129" s="111">
         <f>Legend!$C$9+15</f>
-        <v>46311</v>
+        <v>46116</v>
       </c>
       <c r="D129" s="111" t="s">
         <v>277</v>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="C130" s="110">
         <f>Legend!$C$9+30</f>
-        <v>46326</v>
+        <v>46131</v>
       </c>
       <c r="D130" s="110" t="s">
         <v>275</v>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C131" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D131" s="96" t="s">
         <v>275</v>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="C132" s="98">
         <f>Legend!$C$11-15</f>
-        <v>46342</v>
+        <v>46115</v>
       </c>
       <c r="D132" s="98" t="s">
         <v>275</v>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="C133" s="99">
         <f>Legend!$C$11-7</f>
-        <v>46350</v>
+        <v>46123</v>
       </c>
       <c r="D133" s="99" t="s">
         <v>275</v>
@@ -5735,7 +5735,7 @@
       </c>
       <c r="C134" s="100">
         <f>Legend!$C$11-1</f>
-        <v>46356</v>
+        <v>46129</v>
       </c>
       <c r="D134" s="100" t="s">
         <v>275</v>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="C135" s="101">
         <f>Legend!$C$11</f>
-        <v>46357</v>
+        <v>46130</v>
       </c>
       <c r="D135" s="101" t="s">
         <v>275</v>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="C140" s="112">
         <f>Legend!$C$9</f>
-        <v>46296</v>
+        <v>46101</v>
       </c>
       <c r="D140" s="112" t="s">
         <v>274</v>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C141" s="95">
         <f>Legend!$C$9+7</f>
-        <v>46303</v>
+        <v>46108</v>
       </c>
       <c r="D141" s="95" t="s">
         <v>274</v>
@@ -5895,7 +5895,7 @@
       </c>
       <c r="C142" s="111">
         <f>Legend!$C$9+15</f>
-        <v>46311</v>
+        <v>46116</v>
       </c>
       <c r="D142" s="111" t="s">
         <v>277</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C143" s="110">
         <f>Legend!$C$9+30</f>
-        <v>46326</v>
+        <v>46131</v>
       </c>
       <c r="D143" s="110" t="s">
         <v>277</v>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="C144" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D144" s="96" t="s">
         <v>277</v>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="C145" s="99">
         <f>Legend!$C$11-7</f>
-        <v>46350</v>
+        <v>46123</v>
       </c>
       <c r="D145" s="99" t="s">
         <v>275</v>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="C146" s="100">
         <f>Legend!$C$11-1</f>
-        <v>46356</v>
+        <v>46129</v>
       </c>
       <c r="D146" s="100" t="s">
         <v>275</v>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="C147" s="101">
         <f>Legend!$C$11</f>
-        <v>46357</v>
+        <v>46130</v>
       </c>
       <c r="D147" s="101" t="s">
         <v>275</v>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="C152" s="111">
         <f>Legend!$C$9+15</f>
-        <v>46311</v>
+        <v>46116</v>
       </c>
       <c r="D152" s="111" t="s">
         <v>277</v>
@@ -6136,7 +6136,7 @@
       </c>
       <c r="C153" s="110">
         <f>Legend!$C$9+30</f>
-        <v>46326</v>
+        <v>46131</v>
       </c>
       <c r="D153" s="110" t="s">
         <v>277</v>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="C154" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D154" s="96" t="s">
         <v>275</v>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="C155" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D155" s="96" t="s">
         <v>275</v>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="C156" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D156" s="96" t="s">
         <v>275</v>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="C157" s="98">
         <f>Legend!$C$11-15</f>
-        <v>46342</v>
+        <v>46115</v>
       </c>
       <c r="D157" s="98" t="s">
         <v>275</v>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="C158" s="100">
         <f>Legend!$C$11-1</f>
-        <v>46356</v>
+        <v>46129</v>
       </c>
       <c r="D158" s="100" t="s">
         <v>275</v>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C159" s="101">
         <f>Legend!$C$11</f>
-        <v>46357</v>
+        <v>46130</v>
       </c>
       <c r="D159" s="101" t="s">
         <v>275</v>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="C160" s="101">
         <f>Legend!$C$11</f>
-        <v>46357</v>
+        <v>46130</v>
       </c>
       <c r="D160" s="101" t="s">
         <v>275</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="C161" s="101">
         <f>Legend!$C$11</f>
-        <v>46357</v>
+        <v>46130</v>
       </c>
       <c r="D161" s="101" t="s">
         <v>275</v>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="C162" s="102">
         <f>Legend!$C$12+7</f>
-        <v>46375</v>
+        <v>46241</v>
       </c>
       <c r="D162" s="102" t="s">
         <v>275</v>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="C167" s="112">
         <f>Legend!$C$9</f>
-        <v>46296</v>
+        <v>46101</v>
       </c>
       <c r="D167" s="112" t="s">
         <v>276</v>
@@ -6485,7 +6485,7 @@
       </c>
       <c r="C168" s="111">
         <f>Legend!$C$9+15</f>
-        <v>46311</v>
+        <v>46116</v>
       </c>
       <c r="D168" s="111" t="s">
         <v>276</v>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="C169" s="110">
         <f>Legend!$C$9+30</f>
-        <v>46326</v>
+        <v>46131</v>
       </c>
       <c r="D169" s="110" t="s">
         <v>276</v>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="C170" s="113">
         <f>Legend!$C$11-60</f>
-        <v>46297</v>
+        <v>46070</v>
       </c>
       <c r="D170" s="113" t="s">
         <v>276</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C171" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D171" s="96" t="s">
         <v>277</v>
@@ -6593,7 +6593,7 @@
       </c>
       <c r="C172" s="98">
         <f>Legend!$C$11-15</f>
-        <v>46342</v>
+        <v>46115</v>
       </c>
       <c r="D172" s="98" t="s">
         <v>277</v>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="C173" s="99">
         <f>Legend!$C$11-7</f>
-        <v>46350</v>
+        <v>46123</v>
       </c>
       <c r="D173" s="99" t="s">
         <v>275</v>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="C174" s="100">
         <f>Legend!$C$11-1</f>
-        <v>46356</v>
+        <v>46129</v>
       </c>
       <c r="D174" s="100" t="s">
         <v>275</v>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="C175" s="101">
         <f>Legend!$C$11</f>
-        <v>46357</v>
+        <v>46130</v>
       </c>
       <c r="D175" s="101" t="s">
         <v>275</v>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="C176" s="101">
         <f>Legend!$C$11</f>
-        <v>46357</v>
+        <v>46130</v>
       </c>
       <c r="D176" s="101" t="s">
         <v>275</v>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="C177" s="102">
         <f>Legend!$C$12+7</f>
-        <v>46375</v>
+        <v>46241</v>
       </c>
       <c r="D177" s="102" t="s">
         <v>275</v>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="C197" s="117">
         <f>Legend!$C$12+15</f>
-        <v>46383</v>
+        <v>46249</v>
       </c>
       <c r="D197" s="117" t="s">
         <v>275</v>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="C198" s="117">
         <f>Legend!$C$12+15</f>
-        <v>46383</v>
+        <v>46249</v>
       </c>
       <c r="D198" s="117" t="s">
         <v>275</v>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="C199" s="117">
         <f>Legend!$C$12+15</f>
-        <v>46383</v>
+        <v>46249</v>
       </c>
       <c r="D199" s="117" t="s">
         <v>275</v>
@@ -7143,7 +7143,7 @@
       </c>
       <c r="C200" s="117">
         <f>Legend!$C$12+15</f>
-        <v>46383</v>
+        <v>46249</v>
       </c>
       <c r="D200" s="117" t="s">
         <v>275</v>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="C201" s="117">
         <f>Legend!$C$12+15</f>
-        <v>46383</v>
+        <v>46249</v>
       </c>
       <c r="D201" s="117" t="s">
         <v>275</v>
@@ -7217,14 +7217,14 @@
       <c r="H204" s="61"/>
     </row>
     <row r="206" spans="1:8" ht="15">
-      <c r="A206" s="139" t="s">
+      <c r="A206" s="136" t="s">
         <v>166</v>
       </c>
-      <c r="B206" s="139"/>
-      <c r="C206" s="139"/>
-      <c r="D206" s="139"/>
-      <c r="E206" s="139"/>
-      <c r="F206" s="139"/>
+      <c r="B206" s="136"/>
+      <c r="C206" s="136"/>
+      <c r="D206" s="136"/>
+      <c r="E206" s="136"/>
+      <c r="F206" s="136"/>
     </row>
     <row r="207" spans="1:8" s="47" customFormat="1" ht="15">
       <c r="A207" s="48" t="s">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="C5" s="83">
         <f>Legend!$C$5</f>
-        <v>46266</v>
+        <v>46082</v>
       </c>
       <c r="D5" s="83" t="s">
         <v>274</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="C6" s="84">
         <f>Legend!$C$5+1</f>
-        <v>46267</v>
+        <v>46083</v>
       </c>
       <c r="D6" s="84" t="s">
         <v>274</v>
@@ -7457,7 +7457,7 @@
       </c>
       <c r="C7" s="84">
         <f>Legend!$C$5+1</f>
-        <v>46267</v>
+        <v>46083</v>
       </c>
       <c r="D7" s="84" t="s">
         <v>274</v>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="C8" s="85">
         <f>Legend!$C$5+7</f>
-        <v>46273</v>
+        <v>46089</v>
       </c>
       <c r="D8" s="85" t="s">
         <v>274</v>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="C9" s="85">
         <f>Legend!$C$5+7</f>
-        <v>46273</v>
+        <v>46089</v>
       </c>
       <c r="D9" s="85" t="s">
         <v>274</v>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="C10" s="89">
         <f>Legend!$C$7</f>
-        <v>46280</v>
+        <v>46096</v>
       </c>
       <c r="D10" s="89" t="s">
         <v>274</v>
@@ -7565,7 +7565,7 @@
       </c>
       <c r="C11" s="90">
         <f>Legend!$C$7+15</f>
-        <v>46295</v>
+        <v>46111</v>
       </c>
       <c r="D11" s="90" t="s">
         <v>274</v>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="C15" s="92">
         <f>Legend!$C$11-90</f>
-        <v>46267</v>
+        <v>46040</v>
       </c>
       <c r="D15" s="92" t="s">
         <v>277</v>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="C16" s="92">
         <f>Legend!$C$11-90</f>
-        <v>46267</v>
+        <v>46040</v>
       </c>
       <c r="D16" s="92" t="s">
         <v>277</v>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="C20" s="92">
         <f>Legend!$C$11-90</f>
-        <v>46267</v>
+        <v>46040</v>
       </c>
       <c r="D20" s="92" t="s">
         <v>277</v>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="C21" s="93">
         <f>Legend!$C$9+1</f>
-        <v>46297</v>
+        <v>46102</v>
       </c>
       <c r="D21" s="93" t="s">
         <v>277</v>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C22" s="95">
         <f>Legend!$C$9+3</f>
-        <v>46299</v>
+        <v>46104</v>
       </c>
       <c r="D22" s="95" t="s">
         <v>277</v>
@@ -7787,7 +7787,7 @@
       </c>
       <c r="C23" s="95">
         <f>Legend!$C$9+7</f>
-        <v>46303</v>
+        <v>46108</v>
       </c>
       <c r="D23" s="95" t="s">
         <v>277</v>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="C24" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D24" s="96" t="s">
         <v>277</v>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="C25" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D25" s="96" t="s">
         <v>277</v>
@@ -7882,7 +7882,7 @@
       <c r="B27" s="34"/>
       <c r="C27" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D27" s="96" t="s">
         <v>277</v>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="C28" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D28" s="96" t="s">
         <v>277</v>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C29" s="98">
         <f>Legend!$C$11-15</f>
-        <v>46342</v>
+        <v>46115</v>
       </c>
       <c r="D29" s="98" t="s">
         <v>275</v>
@@ -7955,7 +7955,7 @@
       </c>
       <c r="C30" s="99">
         <f>Legend!$C$11-7</f>
-        <v>46350</v>
+        <v>46123</v>
       </c>
       <c r="D30" s="99" t="s">
         <v>275</v>
@@ -7982,7 +7982,7 @@
       </c>
       <c r="C31" s="100">
         <f>Legend!$C$11-1</f>
-        <v>46356</v>
+        <v>46129</v>
       </c>
       <c r="D31" s="100" t="s">
         <v>275</v>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="C32" s="102">
         <f>Legend!$C$12</f>
-        <v>46368</v>
+        <v>46234</v>
       </c>
       <c r="D32" s="102" t="s">
         <v>275</v>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="C33" s="102">
         <f>Legend!$C$12</f>
-        <v>46368</v>
+        <v>46234</v>
       </c>
       <c r="D33" s="102" t="s">
         <v>275</v>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="C38" s="103">
         <f>Legend!$C$5+45</f>
-        <v>46311</v>
+        <v>46127</v>
       </c>
       <c r="D38" s="103" t="s">
         <v>274</v>
@@ -8148,7 +8148,7 @@
       </c>
       <c r="C39" s="133">
         <f>Legend!$C$5+45</f>
-        <v>46311</v>
+        <v>46127</v>
       </c>
       <c r="D39" s="133" t="s">
         <v>274</v>
@@ -8224,7 +8224,7 @@
       </c>
       <c r="C44" s="106">
         <f>Legend!$C$11-7</f>
-        <v>46350</v>
+        <v>46123</v>
       </c>
       <c r="D44" s="106" t="s">
         <v>277</v>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="C48" s="93">
         <f>Legend!$C$9+1</f>
-        <v>46297</v>
+        <v>46102</v>
       </c>
       <c r="D48" s="93" t="s">
         <v>277</v>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="C49" s="93">
         <f>Legend!$C$9+1</f>
-        <v>46297</v>
+        <v>46102</v>
       </c>
       <c r="D49" s="93" t="s">
         <v>277</v>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="C50" s="110">
         <f>Legend!$C$9+30</f>
-        <v>46326</v>
+        <v>46131</v>
       </c>
       <c r="D50" s="110" t="s">
         <v>275</v>
@@ -8370,7 +8370,7 @@
       </c>
       <c r="C51" s="98">
         <f>Legend!$C$11-15</f>
-        <v>46342</v>
+        <v>46115</v>
       </c>
       <c r="D51" s="98" t="s">
         <v>275</v>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="C55" s="93">
         <f>Legend!$C$9+1</f>
-        <v>46297</v>
+        <v>46102</v>
       </c>
       <c r="D55" s="93" t="s">
         <v>275</v>
@@ -8456,7 +8456,7 @@
       </c>
       <c r="C56" s="95">
         <f>Legend!$C$9+7</f>
-        <v>46303</v>
+        <v>46108</v>
       </c>
       <c r="D56" s="95" t="s">
         <v>275</v>
@@ -8483,7 +8483,7 @@
       </c>
       <c r="C57" s="111">
         <f>Legend!$C$9+15</f>
-        <v>46311</v>
+        <v>46116</v>
       </c>
       <c r="D57" s="111" t="s">
         <v>275</v>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="C61" s="93">
         <f>Legend!$C$9+1</f>
-        <v>46297</v>
+        <v>46102</v>
       </c>
       <c r="D61" s="93" t="s">
         <v>277</v>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="C62" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D62" s="96" t="s">
         <v>277</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C63" s="99">
         <f>Legend!$C$11-7</f>
-        <v>46350</v>
+        <v>46123</v>
       </c>
       <c r="D63" s="99" t="s">
         <v>275</v>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="C64" s="99">
         <f>Legend!$C$11-7</f>
-        <v>46350</v>
+        <v>46123</v>
       </c>
       <c r="D64" s="99" t="s">
         <v>275</v>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="C68" s="93">
         <f>Legend!$C$9+1</f>
-        <v>46297</v>
+        <v>46102</v>
       </c>
       <c r="D68" s="93" t="s">
         <v>274</v>
@@ -8709,7 +8709,7 @@
       </c>
       <c r="C69" s="111">
         <f>Legend!$C$9+15</f>
-        <v>46311</v>
+        <v>46116</v>
       </c>
       <c r="D69" s="111" t="s">
         <v>277</v>
@@ -8736,7 +8736,7 @@
       </c>
       <c r="C70" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D70" s="96" t="s">
         <v>275</v>
@@ -8763,7 +8763,7 @@
       </c>
       <c r="C71" s="98">
         <f>Legend!$C$11-15</f>
-        <v>46342</v>
+        <v>46115</v>
       </c>
       <c r="D71" s="98" t="s">
         <v>275</v>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="C75" s="112">
         <f>Legend!$C$9</f>
-        <v>46296</v>
+        <v>46101</v>
       </c>
       <c r="D75" s="112" t="s">
         <v>277</v>
@@ -8839,7 +8839,7 @@
       </c>
       <c r="C76" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D76" s="96" t="s">
         <v>277</v>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="C77" s="98">
         <f>Legend!$C$11-15</f>
-        <v>46342</v>
+        <v>46115</v>
       </c>
       <c r="D77" s="98" t="s">
         <v>275</v>
@@ -8893,7 +8893,7 @@
       </c>
       <c r="C78" s="99">
         <f>Legend!$C$11-7</f>
-        <v>46350</v>
+        <v>46123</v>
       </c>
       <c r="D78" s="99" t="s">
         <v>275</v>
@@ -8952,7 +8952,7 @@
       </c>
       <c r="C82" s="112">
         <f>Legend!$C$9</f>
-        <v>46296</v>
+        <v>46101</v>
       </c>
       <c r="D82" s="112" t="s">
         <v>277</v>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="C83" s="95">
         <f>Legend!$C$9+7</f>
-        <v>46303</v>
+        <v>46108</v>
       </c>
       <c r="D83" s="95" t="s">
         <v>277</v>
@@ -9006,7 +9006,7 @@
       </c>
       <c r="C84" s="111">
         <f>Legend!$C$9+15</f>
-        <v>46311</v>
+        <v>46116</v>
       </c>
       <c r="D84" s="111" t="s">
         <v>277</v>
@@ -9033,7 +9033,7 @@
       </c>
       <c r="C85" s="110">
         <f>Legend!$C$9+30</f>
-        <v>46326</v>
+        <v>46131</v>
       </c>
       <c r="D85" s="110" t="s">
         <v>275</v>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="C86" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D86" s="96" t="s">
         <v>275</v>
@@ -9087,7 +9087,7 @@
       </c>
       <c r="C87" s="98">
         <f>Legend!$C$11-15</f>
-        <v>46342</v>
+        <v>46115</v>
       </c>
       <c r="D87" s="98" t="s">
         <v>275</v>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="C88" s="99">
         <f>Legend!$C$11-7</f>
-        <v>46350</v>
+        <v>46123</v>
       </c>
       <c r="D88" s="99" t="s">
         <v>275</v>
@@ -9141,7 +9141,7 @@
       </c>
       <c r="C89" s="100">
         <f>Legend!$C$11-1</f>
-        <v>46356</v>
+        <v>46129</v>
       </c>
       <c r="D89" s="100" t="s">
         <v>275</v>
@@ -9160,13 +9160,13 @@
       </c>
     </row>
     <row r="90" spans="1:8" ht="19.899999999999999" customHeight="1">
-      <c r="A90" s="136" t="s">
+      <c r="A90" s="137" t="s">
         <v>297</v>
       </c>
-      <c r="B90" s="137"/>
-      <c r="C90" s="137"/>
-      <c r="D90" s="137"/>
-      <c r="E90" s="138"/>
+      <c r="B90" s="138"/>
+      <c r="C90" s="138"/>
+      <c r="D90" s="138"/>
+      <c r="E90" s="139"/>
       <c r="F90" s="20" t="s">
         <v>0</v>
       </c>
@@ -9214,7 +9214,7 @@
       </c>
       <c r="C94" s="111">
         <f>Legend!$C$9+15</f>
-        <v>46311</v>
+        <v>46116</v>
       </c>
       <c r="D94" s="111" t="s">
         <v>277</v>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="C95" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D95" s="96" t="s">
         <v>277</v>
@@ -9300,7 +9300,7 @@
       </c>
       <c r="C99" s="111">
         <f>Legend!$C$9+15</f>
-        <v>46311</v>
+        <v>46116</v>
       </c>
       <c r="D99" s="111" t="s">
         <v>277</v>
@@ -9327,7 +9327,7 @@
       </c>
       <c r="C100" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D100" s="96" t="s">
         <v>275</v>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="C101" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D101" s="96" t="s">
         <v>275</v>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="C102" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D102" s="96" t="s">
         <v>275</v>
@@ -9408,7 +9408,7 @@
       </c>
       <c r="C103" s="98">
         <f>Legend!$C$11-15</f>
-        <v>46342</v>
+        <v>46115</v>
       </c>
       <c r="D103" s="98" t="s">
         <v>275</v>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="C104" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D104" s="96" t="s">
         <v>275</v>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="C112" s="117">
         <f>Legend!$C$12+15</f>
-        <v>46383</v>
+        <v>46249</v>
       </c>
       <c r="D112" s="117" t="s">
         <v>275</v>
@@ -9571,7 +9571,7 @@
       </c>
       <c r="C113" s="117">
         <f>Legend!$C$12+15</f>
-        <v>46383</v>
+        <v>46249</v>
       </c>
       <c r="D113" s="117" t="s">
         <v>275</v>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="C114" s="117">
         <f>Legend!$C$12+15</f>
-        <v>46383</v>
+        <v>46249</v>
       </c>
       <c r="D114" s="117" t="s">
         <v>275</v>
@@ -9613,7 +9613,7 @@
       </c>
       <c r="C115" s="117">
         <f>Legend!$C$12+15</f>
-        <v>46383</v>
+        <v>46249</v>
       </c>
       <c r="D115" s="117" t="s">
         <v>275</v>
@@ -9634,7 +9634,7 @@
       </c>
       <c r="C116" s="117">
         <f>Legend!$C$12+15</f>
-        <v>46383</v>
+        <v>46249</v>
       </c>
       <c r="D116" s="117" t="s">
         <v>275</v>
@@ -9687,14 +9687,14 @@
       <c r="H119" s="61"/>
     </row>
     <row r="121" spans="1:8" ht="15">
-      <c r="A121" s="139" t="s">
+      <c r="A121" s="136" t="s">
         <v>166</v>
       </c>
-      <c r="B121" s="139"/>
-      <c r="C121" s="139"/>
-      <c r="D121" s="139"/>
-      <c r="E121" s="139"/>
-      <c r="F121" s="139"/>
+      <c r="B121" s="136"/>
+      <c r="C121" s="136"/>
+      <c r="D121" s="136"/>
+      <c r="E121" s="136"/>
+      <c r="F121" s="136"/>
     </row>
     <row r="122" spans="1:8" s="47" customFormat="1" ht="15">
       <c r="A122" s="48" t="s">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="C5" s="83">
         <f>Legend!$C$5</f>
-        <v>46266</v>
+        <v>46082</v>
       </c>
       <c r="D5" s="83" t="s">
         <v>274</v>
@@ -9908,7 +9908,7 @@
       </c>
       <c r="C6" s="84">
         <f>Legend!$C$5+1</f>
-        <v>46267</v>
+        <v>46083</v>
       </c>
       <c r="D6" s="84" t="s">
         <v>274</v>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="C7" s="84">
         <f>Legend!$C$5+1</f>
-        <v>46267</v>
+        <v>46083</v>
       </c>
       <c r="D7" s="84" t="s">
         <v>274</v>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="C8" s="85">
         <f>Legend!$C$5+7</f>
-        <v>46273</v>
+        <v>46089</v>
       </c>
       <c r="D8" s="85" t="s">
         <v>274</v>
@@ -9989,7 +9989,7 @@
       </c>
       <c r="C9" s="85">
         <f>Legend!$C$5+7</f>
-        <v>46273</v>
+        <v>46089</v>
       </c>
       <c r="D9" s="85" t="s">
         <v>274</v>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="C10" s="89">
         <f>Legend!$C$7</f>
-        <v>46280</v>
+        <v>46096</v>
       </c>
       <c r="D10" s="89" t="s">
         <v>274</v>
@@ -10043,7 +10043,7 @@
       </c>
       <c r="C11" s="90">
         <f>Legend!$C$7+15</f>
-        <v>46295</v>
+        <v>46111</v>
       </c>
       <c r="D11" s="90" t="s">
         <v>274</v>
@@ -10105,7 +10105,7 @@
       </c>
       <c r="C15" s="92">
         <f>Legend!$C$11-90</f>
-        <v>46267</v>
+        <v>46040</v>
       </c>
       <c r="D15" s="92" t="s">
         <v>277</v>
@@ -10132,7 +10132,7 @@
       </c>
       <c r="C16" s="92">
         <f>Legend!$C$11-90</f>
-        <v>46267</v>
+        <v>46040</v>
       </c>
       <c r="D16" s="92" t="s">
         <v>277</v>
@@ -10190,7 +10190,7 @@
       </c>
       <c r="C20" s="92">
         <f>Legend!$C$11-90</f>
-        <v>46267</v>
+        <v>46040</v>
       </c>
       <c r="D20" s="92" t="s">
         <v>277</v>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="C21" s="93">
         <f>Legend!$C$9+1</f>
-        <v>46297</v>
+        <v>46102</v>
       </c>
       <c r="D21" s="93" t="s">
         <v>277</v>
@@ -10244,7 +10244,7 @@
       </c>
       <c r="C22" s="95">
         <f>Legend!$C$9+3</f>
-        <v>46299</v>
+        <v>46104</v>
       </c>
       <c r="D22" s="95" t="s">
         <v>277</v>
@@ -10265,7 +10265,7 @@
       </c>
       <c r="C23" s="95">
         <f>Legend!$C$9+7</f>
-        <v>46303</v>
+        <v>46108</v>
       </c>
       <c r="D23" s="95" t="s">
         <v>277</v>
@@ -10292,7 +10292,7 @@
       </c>
       <c r="C24" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D24" s="96" t="s">
         <v>277</v>
@@ -10319,7 +10319,7 @@
       </c>
       <c r="C25" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D25" s="96" t="s">
         <v>277</v>
@@ -10360,7 +10360,7 @@
       <c r="B27" s="34"/>
       <c r="C27" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D27" s="96" t="s">
         <v>277</v>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="C28" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D28" s="96" t="s">
         <v>277</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C29" s="98">
         <f>Legend!$C$11-15</f>
-        <v>46342</v>
+        <v>46115</v>
       </c>
       <c r="D29" s="98" t="s">
         <v>275</v>
@@ -10433,7 +10433,7 @@
       </c>
       <c r="C30" s="99">
         <f>Legend!$C$11-7</f>
-        <v>46350</v>
+        <v>46123</v>
       </c>
       <c r="D30" s="99" t="s">
         <v>275</v>
@@ -10460,7 +10460,7 @@
       </c>
       <c r="C31" s="100">
         <f>Legend!$C$11-1</f>
-        <v>46356</v>
+        <v>46129</v>
       </c>
       <c r="D31" s="100" t="s">
         <v>275</v>
@@ -10487,7 +10487,7 @@
       </c>
       <c r="C32" s="102">
         <f>Legend!$C$12</f>
-        <v>46368</v>
+        <v>46234</v>
       </c>
       <c r="D32" s="102" t="s">
         <v>275</v>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="C33" s="102">
         <f>Legend!$C$12</f>
-        <v>46368</v>
+        <v>46234</v>
       </c>
       <c r="D33" s="102" t="s">
         <v>275</v>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="C38" s="103">
         <f>Legend!$C$5+45</f>
-        <v>46311</v>
+        <v>46127</v>
       </c>
       <c r="D38" s="103" t="s">
         <v>274</v>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="C39" s="133">
         <f>Legend!$C$5+45</f>
-        <v>46311</v>
+        <v>46127</v>
       </c>
       <c r="D39" s="133" t="s">
         <v>274</v>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="C44" s="106">
         <f>Legend!$C$11-7</f>
-        <v>46350</v>
+        <v>46123</v>
       </c>
       <c r="D44" s="106" t="s">
         <v>277</v>
@@ -10767,7 +10767,7 @@
       </c>
       <c r="C48" s="93">
         <f>Legend!$C$9+1</f>
-        <v>46297</v>
+        <v>46102</v>
       </c>
       <c r="D48" s="93" t="s">
         <v>277</v>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="C49" s="93">
         <f>Legend!$C$9+1</f>
-        <v>46297</v>
+        <v>46102</v>
       </c>
       <c r="D49" s="93" t="s">
         <v>277</v>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="C50" s="110">
         <f>Legend!$C$9+30</f>
-        <v>46326</v>
+        <v>46131</v>
       </c>
       <c r="D50" s="110" t="s">
         <v>275</v>
@@ -10848,7 +10848,7 @@
       </c>
       <c r="C51" s="98">
         <f>Legend!$C$11-15</f>
-        <v>46342</v>
+        <v>46115</v>
       </c>
       <c r="D51" s="98" t="s">
         <v>275</v>
@@ -10907,7 +10907,7 @@
       </c>
       <c r="C55" s="93">
         <f>Legend!$C$9+1</f>
-        <v>46297</v>
+        <v>46102</v>
       </c>
       <c r="D55" s="93" t="s">
         <v>275</v>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C56" s="95">
         <f>Legend!$C$9+7</f>
-        <v>46303</v>
+        <v>46108</v>
       </c>
       <c r="D56" s="95" t="s">
         <v>275</v>
@@ -10961,7 +10961,7 @@
       </c>
       <c r="C57" s="111">
         <f>Legend!$C$9+15</f>
-        <v>46311</v>
+        <v>46116</v>
       </c>
       <c r="D57" s="111" t="s">
         <v>275</v>
@@ -11020,7 +11020,7 @@
       </c>
       <c r="C61" s="93">
         <f>Legend!$C$9+1</f>
-        <v>46297</v>
+        <v>46102</v>
       </c>
       <c r="D61" s="93" t="s">
         <v>277</v>
@@ -11047,7 +11047,7 @@
       </c>
       <c r="C62" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D62" s="96" t="s">
         <v>277</v>
@@ -11074,7 +11074,7 @@
       </c>
       <c r="C63" s="99">
         <f>Legend!$C$11-7</f>
-        <v>46350</v>
+        <v>46123</v>
       </c>
       <c r="D63" s="99" t="s">
         <v>275</v>
@@ -11101,7 +11101,7 @@
       </c>
       <c r="C64" s="99">
         <f>Legend!$C$11-7</f>
-        <v>46350</v>
+        <v>46123</v>
       </c>
       <c r="D64" s="99" t="s">
         <v>275</v>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="C68" s="93">
         <f>Legend!$C$9+1</f>
-        <v>46297</v>
+        <v>46102</v>
       </c>
       <c r="D68" s="93" t="s">
         <v>274</v>
@@ -11187,7 +11187,7 @@
       </c>
       <c r="C69" s="111">
         <f>Legend!$C$9+15</f>
-        <v>46311</v>
+        <v>46116</v>
       </c>
       <c r="D69" s="111" t="s">
         <v>277</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C70" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D70" s="96" t="s">
         <v>275</v>
@@ -11241,7 +11241,7 @@
       </c>
       <c r="C71" s="98">
         <f>Legend!$C$11-15</f>
-        <v>46342</v>
+        <v>46115</v>
       </c>
       <c r="D71" s="98" t="s">
         <v>275</v>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="C75" s="112">
         <f>Legend!$C$9</f>
-        <v>46296</v>
+        <v>46101</v>
       </c>
       <c r="D75" s="112" t="s">
         <v>277</v>
@@ -11317,7 +11317,7 @@
       </c>
       <c r="C76" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D76" s="96" t="s">
         <v>277</v>
@@ -11344,7 +11344,7 @@
       </c>
       <c r="C77" s="98">
         <f>Legend!$C$11-15</f>
-        <v>46342</v>
+        <v>46115</v>
       </c>
       <c r="D77" s="98" t="s">
         <v>275</v>
@@ -11371,7 +11371,7 @@
       </c>
       <c r="C78" s="99">
         <f>Legend!$C$11-7</f>
-        <v>46350</v>
+        <v>46123</v>
       </c>
       <c r="D78" s="99" t="s">
         <v>275</v>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="C82" s="112">
         <f>Legend!$C$9</f>
-        <v>46296</v>
+        <v>46101</v>
       </c>
       <c r="D82" s="112" t="s">
         <v>277</v>
@@ -11457,7 +11457,7 @@
       </c>
       <c r="C83" s="95">
         <f>Legend!$C$9+7</f>
-        <v>46303</v>
+        <v>46108</v>
       </c>
       <c r="D83" s="95" t="s">
         <v>277</v>
@@ -11484,7 +11484,7 @@
       </c>
       <c r="C84" s="111">
         <f>Legend!$C$9+15</f>
-        <v>46311</v>
+        <v>46116</v>
       </c>
       <c r="D84" s="111" t="s">
         <v>277</v>
@@ -11511,7 +11511,7 @@
       </c>
       <c r="C85" s="110">
         <f>Legend!$C$9+30</f>
-        <v>46326</v>
+        <v>46131</v>
       </c>
       <c r="D85" s="110" t="s">
         <v>275</v>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="C86" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D86" s="96" t="s">
         <v>275</v>
@@ -11565,7 +11565,7 @@
       </c>
       <c r="C87" s="98">
         <f>Legend!$C$11-15</f>
-        <v>46342</v>
+        <v>46115</v>
       </c>
       <c r="D87" s="98" t="s">
         <v>275</v>
@@ -11592,7 +11592,7 @@
       </c>
       <c r="C88" s="99">
         <f>Legend!$C$11-7</f>
-        <v>46350</v>
+        <v>46123</v>
       </c>
       <c r="D88" s="99" t="s">
         <v>275</v>
@@ -11619,7 +11619,7 @@
       </c>
       <c r="C89" s="100">
         <f>Legend!$C$11-1</f>
-        <v>46356</v>
+        <v>46129</v>
       </c>
       <c r="D89" s="100" t="s">
         <v>275</v>
@@ -11638,13 +11638,13 @@
       </c>
     </row>
     <row r="90" spans="1:8" ht="19.899999999999999" customHeight="1">
-      <c r="A90" s="136" t="s">
+      <c r="A90" s="137" t="s">
         <v>297</v>
       </c>
-      <c r="B90" s="137"/>
-      <c r="C90" s="137"/>
-      <c r="D90" s="137"/>
-      <c r="E90" s="138"/>
+      <c r="B90" s="138"/>
+      <c r="C90" s="138"/>
+      <c r="D90" s="138"/>
+      <c r="E90" s="139"/>
       <c r="F90" s="20" t="s">
         <v>0</v>
       </c>
@@ -11692,7 +11692,7 @@
       </c>
       <c r="C94" s="111">
         <f>Legend!$C$9+15</f>
-        <v>46311</v>
+        <v>46116</v>
       </c>
       <c r="D94" s="111" t="s">
         <v>277</v>
@@ -11719,7 +11719,7 @@
       </c>
       <c r="C95" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D95" s="96" t="s">
         <v>277</v>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="C99" s="111">
         <f>Legend!$C$9+15</f>
-        <v>46311</v>
+        <v>46116</v>
       </c>
       <c r="D99" s="111" t="s">
         <v>277</v>
@@ -11805,7 +11805,7 @@
       </c>
       <c r="C100" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D100" s="96" t="s">
         <v>275</v>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="C101" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D101" s="96" t="s">
         <v>275</v>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="C102" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D102" s="96" t="s">
         <v>275</v>
@@ -11886,7 +11886,7 @@
       </c>
       <c r="C103" s="98">
         <f>Legend!$C$11-15</f>
-        <v>46342</v>
+        <v>46115</v>
       </c>
       <c r="D103" s="98" t="s">
         <v>275</v>
@@ -11913,7 +11913,7 @@
       </c>
       <c r="C104" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D104" s="96" t="s">
         <v>275</v>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C108" s="112">
         <f>Legend!$C$9</f>
-        <v>46296</v>
+        <v>46101</v>
       </c>
       <c r="D108" s="112" t="s">
         <v>276</v>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="C109" s="111">
         <f>Legend!$C$9+15</f>
-        <v>46311</v>
+        <v>46116</v>
       </c>
       <c r="D109" s="111" t="s">
         <v>276</v>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="C110" s="110">
         <f>Legend!$C$9+30</f>
-        <v>46326</v>
+        <v>46131</v>
       </c>
       <c r="D110" s="110" t="s">
         <v>276</v>
@@ -12053,7 +12053,7 @@
       </c>
       <c r="C111" s="113">
         <f>Legend!$C$11-60</f>
-        <v>46297</v>
+        <v>46070</v>
       </c>
       <c r="D111" s="113" t="s">
         <v>276</v>
@@ -12080,7 +12080,7 @@
       </c>
       <c r="C112" s="96">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D112" s="96" t="s">
         <v>277</v>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="C113" s="98">
         <f>Legend!$C$11-15</f>
-        <v>46342</v>
+        <v>46115</v>
       </c>
       <c r="D113" s="98" t="s">
         <v>277</v>
@@ -12134,7 +12134,7 @@
       </c>
       <c r="C114" s="99">
         <f>Legend!$C$11-7</f>
-        <v>46350</v>
+        <v>46123</v>
       </c>
       <c r="D114" s="99" t="s">
         <v>275</v>
@@ -12161,7 +12161,7 @@
       </c>
       <c r="C115" s="100">
         <f>Legend!$C$11-1</f>
-        <v>46356</v>
+        <v>46129</v>
       </c>
       <c r="D115" s="100" t="s">
         <v>275</v>
@@ -12188,7 +12188,7 @@
       </c>
       <c r="C116" s="101">
         <f>Legend!$C$11</f>
-        <v>46357</v>
+        <v>46130</v>
       </c>
       <c r="D116" s="101" t="s">
         <v>275</v>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C117" s="101">
         <f>Legend!$C$11</f>
-        <v>46357</v>
+        <v>46130</v>
       </c>
       <c r="D117" s="101" t="s">
         <v>275</v>
@@ -12242,7 +12242,7 @@
       </c>
       <c r="C118" s="102">
         <f>Legend!$C$12+7</f>
-        <v>46375</v>
+        <v>46241</v>
       </c>
       <c r="D118" s="102" t="s">
         <v>275</v>
@@ -12370,7 +12370,7 @@
       </c>
       <c r="C126" s="117">
         <f>Legend!$C$12+15</f>
-        <v>46383</v>
+        <v>46249</v>
       </c>
       <c r="D126" s="117" t="s">
         <v>275</v>
@@ -12397,7 +12397,7 @@
       </c>
       <c r="C127" s="117">
         <f>Legend!$C$12+15</f>
-        <v>46383</v>
+        <v>46249</v>
       </c>
       <c r="D127" s="117" t="s">
         <v>275</v>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="C128" s="117">
         <f>Legend!$C$12+15</f>
-        <v>46383</v>
+        <v>46249</v>
       </c>
       <c r="D128" s="117" t="s">
         <v>275</v>
@@ -12439,7 +12439,7 @@
       </c>
       <c r="C129" s="117">
         <f>Legend!$C$12+15</f>
-        <v>46383</v>
+        <v>46249</v>
       </c>
       <c r="D129" s="117" t="s">
         <v>275</v>
@@ -12460,7 +12460,7 @@
       </c>
       <c r="C130" s="117">
         <f>Legend!$C$12+15</f>
-        <v>46383</v>
+        <v>46249</v>
       </c>
       <c r="D130" s="117" t="s">
         <v>275</v>
@@ -12513,14 +12513,14 @@
       <c r="H133" s="61"/>
     </row>
     <row r="135" spans="1:8" ht="15">
-      <c r="A135" s="139" t="s">
+      <c r="A135" s="136" t="s">
         <v>166</v>
       </c>
-      <c r="B135" s="139"/>
-      <c r="C135" s="139"/>
-      <c r="D135" s="139"/>
-      <c r="E135" s="139"/>
-      <c r="F135" s="139"/>
+      <c r="B135" s="136"/>
+      <c r="C135" s="136"/>
+      <c r="D135" s="136"/>
+      <c r="E135" s="136"/>
+      <c r="F135" s="136"/>
     </row>
     <row r="136" spans="1:8" s="47" customFormat="1" ht="15">
       <c r="A136" s="48" t="s">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="C5" s="86">
         <f>Legend!$C$5+7</f>
-        <v>46273</v>
+        <v>46089</v>
       </c>
       <c r="D5" s="86" t="s">
         <v>274</v>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="C6" s="86">
         <f>Legend!$C$5+7</f>
-        <v>46273</v>
+        <v>46089</v>
       </c>
       <c r="D6" s="86" t="s">
         <v>274</v>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="C7" s="87">
         <f>Legend!$C$7-1</f>
-        <v>46279</v>
+        <v>46095</v>
       </c>
       <c r="D7" s="87" t="s">
         <v>274</v>
@@ -12732,7 +12732,7 @@
       </c>
       <c r="C8" s="94">
         <f>Legend!$C$9+3</f>
-        <v>46299</v>
+        <v>46104</v>
       </c>
       <c r="D8" s="94" t="s">
         <v>277</v>
@@ -12753,7 +12753,7 @@
       </c>
       <c r="C9" s="97">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D9" s="97" t="s">
         <v>277</v>
@@ -12771,7 +12771,7 @@
       </c>
       <c r="C10" s="97">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D10" s="97" t="s">
         <v>277</v>
@@ -12789,7 +12789,7 @@
       </c>
       <c r="C11" s="104">
         <f>Legend!$C$5+40</f>
-        <v>46306</v>
+        <v>46122</v>
       </c>
       <c r="D11" s="104" t="s">
         <v>274</v>
@@ -12816,7 +12816,7 @@
       </c>
       <c r="C12" s="105">
         <f>Legend!$C$5+35</f>
-        <v>46301</v>
+        <v>46117</v>
       </c>
       <c r="D12" s="105" t="s">
         <v>274</v>
@@ -12843,7 +12843,7 @@
       </c>
       <c r="C13" s="105">
         <f>Legend!$C$5+35</f>
-        <v>46301</v>
+        <v>46117</v>
       </c>
       <c r="D13" s="105" t="s">
         <v>274</v>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="C15" s="99">
         <f>Legend!$C$11-7</f>
-        <v>46350</v>
+        <v>46123</v>
       </c>
       <c r="D15" s="99" t="s">
         <v>275</v>
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C16" s="101">
         <f>Legend!$C$11-7</f>
-        <v>46350</v>
+        <v>46123</v>
       </c>
       <c r="D16" s="101" t="s">
         <v>275</v>
@@ -12909,7 +12909,7 @@
       </c>
       <c r="C19" s="101">
         <f>Legend!$C$11-7</f>
-        <v>46350</v>
+        <v>46123</v>
       </c>
       <c r="D19" s="101" t="s">
         <v>275</v>
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C24" s="106">
         <f>Legend!$C$11-15</f>
-        <v>46342</v>
+        <v>46115</v>
       </c>
       <c r="D24" s="106" t="s">
         <v>277</v>
@@ -13001,7 +13001,7 @@
       </c>
       <c r="C25" s="107">
         <f>Legend!$C$11-7</f>
-        <v>46350</v>
+        <v>46123</v>
       </c>
       <c r="D25" s="107" t="s">
         <v>277</v>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="C26" s="108">
         <f>Legend!$C$11-2</f>
-        <v>46355</v>
+        <v>46128</v>
       </c>
       <c r="D26" s="108" t="s">
         <v>275</v>
@@ -13043,7 +13043,7 @@
       </c>
       <c r="C27" s="108">
         <f>Legend!$C$11-2</f>
-        <v>46355</v>
+        <v>46128</v>
       </c>
       <c r="D27" s="108" t="s">
         <v>275</v>
@@ -13064,7 +13064,7 @@
       </c>
       <c r="C28" s="108">
         <f>Legend!$C$11-2</f>
-        <v>46355</v>
+        <v>46128</v>
       </c>
       <c r="D28" s="108" t="s">
         <v>275</v>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C29" s="108">
         <f>Legend!$C$11-2</f>
-        <v>46355</v>
+        <v>46128</v>
       </c>
       <c r="D29" s="108" t="s">
         <v>275</v>
@@ -13131,7 +13131,7 @@
       </c>
       <c r="C33" s="100">
         <f>Legend!$C$11-1</f>
-        <v>46356</v>
+        <v>46129</v>
       </c>
       <c r="D33" s="100" t="s">
         <v>275</v>
@@ -13163,7 +13163,7 @@
       </c>
       <c r="C36" s="101">
         <f>Legend!$C$11</f>
-        <v>46357</v>
+        <v>46130</v>
       </c>
       <c r="D36" s="101" t="s">
         <v>275</v>
@@ -13195,7 +13195,7 @@
       </c>
       <c r="C40" s="100">
         <f>Legend!$C$11-1</f>
-        <v>46356</v>
+        <v>46129</v>
       </c>
       <c r="D40" s="100" t="s">
         <v>275</v>
@@ -13227,7 +13227,7 @@
       </c>
       <c r="C43" s="100">
         <f>Legend!$C$11-1</f>
-        <v>46356</v>
+        <v>46129</v>
       </c>
       <c r="D43" s="100" t="s">
         <v>275</v>
@@ -13254,7 +13254,7 @@
       </c>
       <c r="C44" s="101">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D44" s="101" t="s">
         <v>275</v>
@@ -13281,7 +13281,7 @@
       </c>
       <c r="C45" s="101">
         <f>Legend!$C$11-30</f>
-        <v>46327</v>
+        <v>46100</v>
       </c>
       <c r="D45" s="101" t="s">
         <v>275</v>
@@ -13313,7 +13313,7 @@
       </c>
       <c r="C48" s="100">
         <f>Legend!$C$11-1</f>
-        <v>46356</v>
+        <v>46129</v>
       </c>
       <c r="D48" s="100" t="s">
         <v>275</v>
@@ -13345,7 +13345,7 @@
       </c>
       <c r="C51" s="100">
         <f>Legend!$C$11-1</f>
-        <v>46356</v>
+        <v>46129</v>
       </c>
       <c r="D51" s="100" t="s">
         <v>275</v>
@@ -13372,7 +13372,7 @@
       </c>
       <c r="C52" s="101">
         <f>Legend!$C$11</f>
-        <v>46357</v>
+        <v>46130</v>
       </c>
       <c r="D52" s="101" t="s">
         <v>275</v>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="C53" s="101">
         <f>Legend!$C$11</f>
-        <v>46357</v>
+        <v>46130</v>
       </c>
       <c r="D53" s="101" t="s">
         <v>275</v>
@@ -13426,7 +13426,7 @@
       </c>
       <c r="C54" s="101">
         <f>Legend!$C$11</f>
-        <v>46357</v>
+        <v>46130</v>
       </c>
       <c r="D54" s="101" t="s">
         <v>275</v>
